--- a/jira_export_2026-07-23.xlsx
+++ b/jira_export_2026-07-23.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>449 h</t>
+          <t>455 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>1512</v>
       </c>
       <c r="P35" s="13" t="n">
-        <v>672</v>
+        <v>604.8</v>
       </c>
     </row>
     <row r="36">
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="K60" s="15" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>4224.5</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>497</v>
+        <v>469.39</v>
       </c>
     </row>
     <row r="61">
@@ -5606,7 +5606,7 @@
         <v>3</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>1057.5</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>384.55</v>
+        <v>325.38</v>
       </c>
     </row>
     <row r="69">
@@ -11406,7 +11406,7 @@
         <v>16</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="L150" s="15" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>36445.07</v>
       </c>
       <c r="P179" s="19" t="n">
-        <v>129.12</v>
+        <v>127.77</v>
       </c>
     </row>
   </sheetData>
@@ -14240,7 +14240,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>154.75</v>
+        <v>155.75</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>33.25</v>
@@ -14249,7 +14249,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>49.75</v>
@@ -14259,7 +14259,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.5%</t>
         </is>
       </c>
     </row>
@@ -14270,7 +14270,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>82.75</v>
+        <v>84.75</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>6.25</v>
@@ -14279,17 +14279,17 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>89.5</v>
+        <v>91.5</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>16.75</v>
+        <v>18.75</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>263.34</v>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.7%</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>96.33</v>
+        <v>97.58</v>
       </c>
     </row>
   </sheetData>
